--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -539,3024 +539,3374 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>allulose</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ING.allulose</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>20.1309</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.7566</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>실측 18건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>sweet↑ body↑</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>arabic_gum</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ING.arabic_gum</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3.3278</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.8038</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>실측 12건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>emulaid</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ING.emulaid</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.8201</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.4423</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>실측 10건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>high_intensity_sweetener</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ING.high_intensity_sweetener</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>실측 1건 모두 같은 수준(0.0556) — 임의 폭, 검토 필요</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sweet↑ body↑</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lactic_acid</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ING.lactic_acid</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2582</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.6098</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>실측 18건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>palm_oil</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ING.palm_oil</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5.0327</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.7416</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>실측 14건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>oiliness↑ body↑ creaminess↑</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rice_bran_emulsifier</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ING.rice_bran_emulsifier</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.2099</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.4646</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>실측 18건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rice_syrup</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ING.rice_syrup</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>54.7945</v>
+      </c>
+      <c r="G9" t="n">
+        <v>64.39149999999999</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>실측 18건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>sweet↑ cooked_rice↑ body↑</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>salt</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ING.salt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>실측 18건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sunflower_oil</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ING.sunflower_oil</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5.8038</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.074400000000001</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>실측 4건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>oiliness↑ rancid_oxidized↑ body↑ creaminess↑</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>vanilla_extract</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ING.vanilla_extract</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.9663</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.1192</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>실측 16건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(실측에서 자동)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>xanthan_gum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ING.xanthan_gum</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>실측 7건의 사용 범위 — 검토 필요</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>body↑</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>슬롯·등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>필수 base</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>쌀 농축액 (rice extract)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ING.rice_extract</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F14" t="n">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G14" t="n">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · 필수 base 13% 고정 부근</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>제품 필수 base — 쌀 풍미+고형분. 내재 당류량 확정 필요(저당 회계)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>코코넛오일 / 정제야자유</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>ING.coconut_oil</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 유지방 대체 주력. 6% 미만이면 크리미가 안 서고, 14% 넘으면 기름진 느낌</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>코코넛오일 / 정제야자유</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>ING.refined_coconut_oil</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G16" t="n">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 정제야자유</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>하이 팻 파우더</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>ING.high_fat_powder</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 분말지방. 믹스 편의</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>분말지방; 믹스 편의·크리미</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>비건크리머 / 프리마</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>ING.vegan_creamer</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 지방+유화 겸. 당을 소량 동반</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>비건크리머 / 프리마</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>ING.prima_creamer</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 프리마. 당 소량 기여를 저당 회계에 반영할 것</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>팜핵경화유</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ING.hydrogenated_palm_kernel_oil</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 경질지방 — 소량 구조재. 과하면 왁시</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>경질지방→용해저항·구조(소량 구조재)</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>팜 정제유</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ING.palm_oil</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 범용 식물지방. 코코넛유보다 보조 위치</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>범용 식물지방</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>현미유</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>ING.rice_bran_oil</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · PUFA 산화 관리 필요 — 상한을 낮게</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>쌀 뉘앙스 보강 가능; PUFA 산화 관리 필요</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>고올레산 해바라기유</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>ING.high_oleic_sunflower_oil</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 산화안정 좋은 액상유</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>산화안정 좋은 액상유</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>일반 해바라기유</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>ING.sunflower_oil</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 산화 취약 — 산화취 위험. 고올레산형으로 대체 권장</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>산화 취약 — 산화취 위험, 지양</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>생크림</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>ING.cream</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>동물성(비건 아님)</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>알룰로스</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>ING.allulose</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F26" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G26" t="n">
         <v>15</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 알룰로스</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>저당 linchpin — 단맛+바디+빙점강하, 쿨링 없음</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>에리스리톨</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>ING.erythritol</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 8% 넘으면 쿨링 오프노트가 뚜렷해진다(HANDOFF 경고)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>보조 감미·FPD; 쿨링 오프노트 주의</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>고감미도 감미료</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>ING.high_intensity_sweetener</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 극소량. 여운·쓴맛이 따라온다</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>단맛 보강 극소량(벌크·FPD 없음)</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>설탕/물엿/포도당/쌀조청</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>ING.sucrose</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 저당 목표와 상충하나 FPD·바디 목적 최소량은 필요할 수 있다</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>설탕/물엿/포도당/쌀조청</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>ING.glucose_syrup</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 같은 이유</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>설탕/물엿/포도당/쌀조청</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>ING.dextrose</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. FPD 가 설탕보다 강해 소량으로도 효과</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>설탕/물엿/포도당/쌀조청</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>ING.rice_syrup</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류(쌀조청)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>분리대두단백</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>ING.soy_protein_isolate</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 유화·기포·바디. 3.5% 넘으면 콩 오프노트</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>유화·기포·바디 (단백 결론: 대두단백)</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>완두단백</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>ING.pea_protein_isolate</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 대체 식물단백. 오프노트는 대두보다 강한 편</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>대체 식물단백</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>쌀단백</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>ING.rice_protein</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 가용성 낮고 그릿티 — 대두단백으로 대체 결론(HANDOFF)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>가용성 낮음·그릿티 → 대두로 대체</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>탈지분유</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>ING.skim_milk_powder</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>동물성(비건 아님)</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>구아검</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>ING.guar_gum</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F37" t="n">
         <v>0.15</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G37" t="n">
         <v>0.35</v>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 구아검</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>얼음결정 억제 주력</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>로커스트빈검(LBG)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>ING.locust_bean_gum</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="F38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 구아와 시너지. 0.3% 넘으면 검성</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>구아와 시너지·크리미</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>카라기난 / 람다</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>ING.carrageenan</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="F39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 2차 안정제 — 유청분리 방지용 극소량</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>카라기난 / 람다</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>ING.lambda_carrageenan</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="F40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 같은 역할. 겔화 안 하는 형</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>AnyAddy An15 (HPMC)</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>ING.anyaddy_an15</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="F41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · HPMC. 오버런·용해저항·동결해동</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓ icy↓</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>오버런·용해저항·동결해동 안정</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>잔탄검</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>ING.xanthan_gum</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="F42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 온톨로지 limitations: '&gt; ~0.5% -&gt; slimy/stringy'. 그보다 훨씬 낮게 잡음</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>소량 점도(과량시 검성 주의)</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>CMC</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>ING.cmc</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 점도·수분결합</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>점도·수분결합</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>겔란검</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>ING.gellan_gum</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="F44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 극소량 구조. 과하면 부서지는 겔</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>icy↓ body↑</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>겔화, 극소량 구조</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>변성전분</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>ING.modified_starch</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 바디·fat replacer. 과하면 전분 느낌</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>바디·fat replacer</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>모노디글리세라이드(MDG)</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>ING.mono_diglycerides</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="F46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 아이스크림 표준 유화제</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>아이스크림 표준 유화제(식물성 선택)</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>DMG95</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>ING.dmg95</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="F47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 저HLB. 총량 0.3% 안팎에서 고HLB와 비율 조절</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>저HLB→지방 부분응집(건조·크리미·용해지연)</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>슈가에스터 S-1670</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>ING.sucrose_ester_s1670</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="F48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 고HLB. DMG95 와 페어링</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>고HLB→미세 유화(저HLB와 페어링)</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>S-1170 / 레시틴 / Soyacell</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>ING.sucrose_ester_s1170</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="F49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 중HLB 보조</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>S-1170 / 레시틴 / Soyacell</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>ING.lecithin</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="F50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>S-1170 / 레시틴 / Soyacell</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>ING.soyacell</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="F51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>에멀에이드 / 현미호분추출분말</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>ING.emulaid</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="F52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 보조 유화</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>에멀에이드 / 현미호분추출분말</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>ING.rice_bran_emulsifier</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="F53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 현미호분추출분말 — 유화 겸 풍미. 음료 실측에서 1.2~2.5% 사용</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>폴리소르베이트80</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>ING.polysorbate_80</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="F54" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 매우 강력하나 라벨 이슈. 쓴다면 극소량</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>creaminess↑</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>매우 강력하나 라벨 이슈</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>이눌린</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>ING.inulin</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 섬유·fat replacer. 과하면 소화 불편</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>섬유·fat replacer·바디(저당 고형분)</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>폴리덱스트로스</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>ING.polydextrose</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 벌킹·약한 FPD. 같은 이유로 상한</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>벌킹·약한 FPD</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>난소화성 말토덱스트린</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>ING.resistant_maltodextrin</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 가용성 섬유. 당류 미산입</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>가용성 섬유·바디(당 아님)</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>결정셀룰로오스(MCC)</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>ING.microcrystalline_cellulose</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="F58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · heat-shock 저항·fat-like</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>heat-shock/용해저항·fat-like</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>말토덱스트린 / 덱스트린</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>ING.maltodextrin</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 고형분. GI 유의</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>말토덱스트린 / 덱스트린</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>ING.dextrin</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 고형분</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>바닐라 추출물</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>ING.vanilla_extract</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="F61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 기본 향</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
         <is>
           <t>기본 향</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>현미 추출분말</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>ING.brown_rice_extract_powder</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="F62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 쌀 풍미 보강</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>쌀 풍미 보강(base와 별개시)</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>소금</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>ING.salt</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="F63" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
         <is>
           <t>풍미증진·리치니스↑(소량)</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>딸기퓨레 / 딸기향</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>ING.strawberry_puree</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시. 수분·당을 동반</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>딸기퓨레 / 딸기향</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>ING.strawberry_artificial</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="F65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>ID 확인 필요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>구연산/무수구연산/젖산</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>ING.citric_acid</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="6" t="inlineStr">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="K54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>구연산/무수구연산/젖산</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>ING.citric_acid_anhydrous</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr"/>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>구연산/무수구연산/젖산</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>ING.lactic_acid</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr"/>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="6" t="inlineStr">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="K56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>탄산칼슘/젖산칼슘/구연산나트륨</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>ING.calcium_carbonate</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
-      <c r="G57" s="6" t="inlineStr"/>
-      <c r="H57" s="6" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr"/>
-      <c r="J57" s="6" t="inlineStr">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="K57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>탄산칼슘/젖산칼슘/구연산나트륨</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>ING.calcium_lactate</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr"/>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="6" t="inlineStr">
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="K58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>탄산칼슘/젖산칼슘/구연산나트륨</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>ING.sodium_citrate</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr"/>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>icy↓</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="K59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>소브산칼륨</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>ING.potassium_sorbate</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr"/>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
         <is>
           <t>보존제(미생물) — 물성 후 단계</t>
         </is>
       </c>
-      <c r="K60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>icecream</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>식물추출물(무효과)</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>ING.plant_extract</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="6" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="6" t="inlineStr">
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
         <is>
           <t>관능·물성 효과 없음</t>
         </is>
       </c>
-      <c r="K61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>allulose</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>ING.allulose</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>20.1309</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>25.7566</v>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>sweet↑ body↑</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr"/>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>arabic_gum</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>ING.arabic_gum</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>3.3278</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>5.8038</v>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>실측 12건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>emulaid</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>ING.emulaid</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>2.8201</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>3.4423</v>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>실측 10건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>high_intensity_sweetener</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>ING.high_intensity_sweetener</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0.0834</v>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>실측 1건 모두 같은 수준(0.0556) — 임의 폭, 검토 필요</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>sweet↑ body↑</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>lactic_acid</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>ING.lactic_acid</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>1.2582</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>1.6098</v>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>palm_oil</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>ING.palm_oil</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>5.0327</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>6.7416</v>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>실측 14건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>oiliness↑ body↑ creaminess↑</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>rice_bran_emulsifier</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>ING.rice_bran_emulsifier</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>1.2099</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>2.4646</v>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr"/>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>rice_syrup</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>ING.rice_syrup</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>54.7945</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>64.39149999999999</v>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>sweet↑ cooked_rice↑ body↑</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr"/>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>salt</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>ING.salt</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>0.6885</v>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr"/>
-      <c r="J70" s="3" t="inlineStr"/>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>sunflower_oil</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>ING.sunflower_oil</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>5.8038</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>9.074400000000001</v>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>실측 4건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>oiliness↑ rancid_oxidized↑ body↑ creaminess↑</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>vanilla_extract</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>ING.vanilla_extract</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>1.9663</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>3.1192</v>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>실측 16건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr"/>
-      <c r="J72" s="3" t="inlineStr"/>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>beverage_rice_milk</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>(실측에서 자동)</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>xanthan_gum</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>ING.xanthan_gum</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.3328</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0.5562</v>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>실측 7건의 사용 범위 — 검토 필요</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>body↑</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr"/>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>슬롯·등급 확인 필요</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3582,9 +3932,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3592,9 +3939,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -3637,9 +3981,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -3661,9 +4002,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -3706,9 +4044,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -3736,9 +4071,6 @@
           <t xml:space="preserve">  '슬롯·등급 확인 필요' — 실측 데이터에서 자동으로 만든 행이다.</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">

--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -613,14 +613,14 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3278</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>5.8038</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>실측 12건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 중 12건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -656,14 +656,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8201</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>3.4423</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>실측 10건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 중 10건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -699,14 +699,14 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0834</v>
+        <v>0.0556</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>실측 1건 모두 같은 수준(0.0556) — 임의 폭, 검토 필요</t>
+          <t>실측 18건 중 1건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -790,14 +790,14 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.0327</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>6.7416</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>실측 14건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 중 14건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>실측 18건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -972,14 +972,14 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.8038</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>9.074400000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>실측 4건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 중 4건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1020,14 +1020,14 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9663</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>3.1192</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>실측 16건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 중 16건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1063,14 +1063,14 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.3328</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0.5562</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>실측 7건의 사용 범위 — 검토 필요</t>
+          <t>실측 18건 중 7건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3932,6 +3932,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3939,6 +3940,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -3981,6 +3983,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -4002,6 +4005,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -4044,6 +4048,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -4072,6 +4077,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>

--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -100,6 +100,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,11 +468,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -489,50 +492,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>온톨로지ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>하한</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>상한</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>범위근거</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>담당축</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
@@ -544,43 +552,43 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>allulose</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>알룰로스</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>ING.allulose</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>20.1309</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>25.7566</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>sweet↑ body↑</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -592,38 +600,38 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>arabic_gum</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ING.arabic_gum</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5.8038</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>실측 18건 중 12건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -635,38 +643,38 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>emulaid</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>에멀에이드</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>ING.emulaid</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>3.4423</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>실측 18건 중 10건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -678,43 +686,43 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>high_intensity_sweetener</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>고감미도 감미료</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ING.high_intensity_sweetener</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.0556</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>실측 18건 중 1건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>sweet↑ body↑</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -726,38 +734,38 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>lactic_acid</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>젖산</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>ING.lactic_acid</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1.2582</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1.6098</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -769,43 +777,43 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>palm_oil</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>팜 정제유</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>ING.palm_oil</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>6.7416</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>실측 18건 중 14건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>oiliness↑ body↑ creaminess↑</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>body↑ creaminess↑</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -817,38 +825,38 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>rice_bran_emulsifier</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>현미호분추출분말</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>ING.rice_bran_emulsifier</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1.2099</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>2.4646</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -860,43 +868,43 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>rice_syrup</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>쌀조청</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ING.rice_syrup</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>54.7945</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>64.39149999999999</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>sweet↑ cooked_rice↑ body↑</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -908,38 +916,38 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>salt</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>소금</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>ING.salt</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.4512</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.6885</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[검토 2026-08-31 · 값 수정]  · 이전: 실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -951,43 +959,43 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>sunflower_oil</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>일반 해바라기유</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>ING.sunflower_oil</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>9.074400000000001</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>실측 18건 중 4건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>oiliness↑ rancid_oxidized↑ body↑ creaminess↑</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>rancid_oxidized↑ body↑ creaminess↑</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -999,38 +1007,38 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>vanilla_extract</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>바닐라 추출물</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>ING.vanilla_extract</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>3.1192</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>실측 18건 중 16건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -1042,43 +1050,43 @@
           <t>beverage_rice_milk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>(실측에서 자동)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>xanthan_gum</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>잔탄검</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>ING.xanthan_gum</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.5562</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>실측 18건 중 7건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -1090,48 +1098,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>필수 base</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>쌀 농축액 (rice extract)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>ING.rice_extract</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>12</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>14</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · 필수 base 13% 고정 부근</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>제품 필수 base — 쌀 풍미+고형분. 내재 당류량 확정 필요(저당 회계)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1139,48 +1148,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>코코넛오일 / 정제야자유</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>코코넛오일</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ING.coconut_oil</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>6</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>14</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 유지방 대체 주력. 6% 미만이면 크리미가 안 서고, 14% 넘으면 기름진 느낌</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1188,48 +1198,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>코코넛오일 / 정제야자유</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>정제야자유</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ING.refined_coconut_oil</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>6</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>14</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 정제야자유</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1237,48 +1248,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>하이 팻 파우더</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>ING.high_fat_powder</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>3</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>10</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 분말지방. 믹스 편의</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>분말지방; 믹스 편의·크리미</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1286,48 +1298,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>비건크리머 / 프리마</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>비건크리머</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>ING.vegan_creamer</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>2</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>8</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 지방+유화 겸. 당을 소량 동반</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>creaminess↑ body↑</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓ body↑</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1335,48 +1348,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>비건크리머 / 프리마</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>프리마</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>ING.prima_creamer</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>8</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 프리마. 당 소량 기여를 저당 회계에 반영할 것</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>creaminess↑ body↑</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓ body↑</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1384,48 +1398,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>팜핵경화유</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>ING.hydrogenated_palm_kernel_oil</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>5</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 경질지방 — 소량 구조재. 과하면 왁시</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>경질지방→용해저항·구조(소량 구조재)</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1433,48 +1448,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>팜 정제유</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>ING.palm_oil</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>4</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>12</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 범용 식물지방. 코코넛유보다 보조 위치</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>범용 식물지방</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1482,48 +1498,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>현미유</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>ING.rice_bran_oil</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>10</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · PUFA 산화 관리 필요 — 상한을 낮게</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>쌀 뉘앙스 보강 가능; PUFA 산화 관리 필요</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1531,48 +1548,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>고올레산 해바라기유</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>ING.high_oleic_sunflower_oil</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>10</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 산화안정 좋은 액상유</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>산화안정 좋은 액상유</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1580,48 +1598,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>일반 해바라기유</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>ING.sunflower_oil</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>8</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 산화 취약 — 산화취 위험. 고올레산형으로 대체 권장</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>산화 취약 — 산화취 위험, 지양</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1629,40 +1648,41 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
         <is>
           <t>지방(유지)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>생크림</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>ING.cream</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>동물성(비건 아님)</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1670,48 +1690,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>알룰로스</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>ING.allulose</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>9</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>15</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 알룰로스</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>저당 linchpin — 단맛+바디+빙점강하, 쿨링 없음</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1719,48 +1740,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>에리스리톨</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>ING.erythritol</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>2</v>
       </c>
-      <c r="G27" t="n">
-        <v>8</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 8% 넘으면 쿨링 오프노트가 뚜렷해진다(HANDOFF 경고)</t>
-        </is>
+      <c r="H27" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · 8% 넘으면 쿨링 오프노트가 뚜렷해진다(HANDOFF 경고)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>보조 감미·FPD; 쿨링 오프노트 주의</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1768,48 +1790,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>고감미도 감미료</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>ING.high_intensity_sweetener</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>옵션</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>0.01</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>0.08</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 극소량. 여운·쓴맛이 따라온다</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 삭제] HIS는 쪼개기로 했었지.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>단맛 보강 극소량(벌크·FPD 없음)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1817,48 +1840,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>설탕/물엿/포도당/쌀조청</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>설탕</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>ING.sucrose</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
       <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 저당 목표와 상충하나 FPD·바디 목적 최소량은 필요할 수 있다</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 값 수정] 목적에 따라 상한/하한이 바뀐다. 지금껀 일반 아이스크림 기준으로, 저당 아이스크림은 상한이 5, 하한은 0이된다. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 저당 목표와 상충하나 FPD·바디 목적 최소량은 필요할 수 있다</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1866,48 +1890,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>설탕/물엿/포도당/쌀조청</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>물엿</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>ING.glucose_syrup</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
       <c r="G30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 같은 이유</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 같은 이유</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1915,48 +1940,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>설탕/물엿/포도당/쌀조청</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>포도당</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>ING.dextrose</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>5</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. FPD 가 설탕보다 강해 소량으로도 효과</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1964,48 +1990,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>감미/빙점</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>설탕/물엿/포도당/쌀조청</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>쌀조청</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>ING.rice_syrup</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
       <c r="G32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류(쌀조청)</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류(쌀조청)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2013,48 +2040,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>분리대두단백</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>ING.soy_protein_isolate</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>3.5</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 유화·기포·바디. 3.5% 넘으면 콩 오프노트</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>유화·기포·바디 (단백 결론: 대두단백)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2062,48 +2090,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>완두단백</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>ING.pea_protein_isolate</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>3.5</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 대체 식물단백. 오프노트는 대두보다 강한 편</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>대체 식물단백</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2111,48 +2140,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>쌀단백</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>ING.rice_protein</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.5</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 가용성 낮고 그릿티 — 대두단백으로 대체 결론(HANDOFF)</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 보류] 쌀단백은 공급사에 따라 편차가 굉장히 큰 재료. 일단 보류 후 데이터에 의존 · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 가용성 낮고 그릿티 — 대두단백으로 대체 결론(HANDOFF)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>가용성 낮음·그릿티 → 대두로 대체</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2160,40 +2190,41 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
         <is>
           <t>단백</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>탈지분유</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>ING.skim_milk_powder</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>동물성(비건 아님)</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2201,48 +2232,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>구아검</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>ING.guar_gum</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>0.15</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>0.35</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 구아검</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>얼음결정 억제 주력</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2250,48 +2282,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>로커스트빈검(LBG)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>ING.locust_bean_gum</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.1</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>0.3</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 구아와 시너지. 0.3% 넘으면 검성</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>구아와 시너지·크리미</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2299,48 +2332,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>카라기난 / 람다</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>카라기난</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>ING.carrageenan</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>0.01</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>0.05</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 2차 안정제 — 유청분리 방지용 극소량</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2348,48 +2382,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>카라기난 / 람다</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>람다</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>ING.lambda_carrageenan</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.01</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0.05</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 같은 역할. 겔화 안 하는 형</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2397,48 +2432,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>AnyAddy An15 (HPMC)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>ING.anyaddy_an15</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.1</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · HPMC. 오버런·용해저항·동결해동</t>
-        </is>
+      <c r="H41" t="n">
+        <v>3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · HPMC. 오버런·용해저항·동결해동</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>creaminess↑ hardness↓ icy↓</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>오버런·용해저항·동결해동 안정</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2446,48 +2482,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>잔탄검</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>ING.xanthan_gum</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>0.05</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>0.2</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 온톨로지 limitations: '&gt; ~0.5% -&gt; slimy/stringy'. 그보다 훨씬 낮게 잡음</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>소량 점도(과량시 검성 주의)</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2495,48 +2532,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>CMC</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>ING.cmc</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>0.1</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>0.3</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 점도·수분결합</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>점도·수분결합</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2544,48 +2582,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>겔란검</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>ING.gellan_gum</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>0.02</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>0.1</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 극소량 구조. 과하면 부서지는 겔</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>icy↓ body↑</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓ body↑</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>겔화, 극소량 구조</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2593,48 +2632,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
         <is>
           <t>안정제</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>변성전분</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>ING.modified_starch</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>4</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 바디·fat replacer. 과하면 전분 느낌</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>바디·fat replacer</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2642,48 +2682,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>모노디글리세라이드(MDG)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>ING.mono_diglycerides</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.1</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 아이스크림 표준 유화제</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 아이스크림 표준 유화제</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↑</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>아이스크림 표준 유화제(식물성 선택)</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2691,48 +2732,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>DMG95</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>ING.dmg95</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>0.05</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>0.25</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 저HLB. 총량 0.3% 안팎에서 고HLB와 비율 조절</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 저HLB. 총량 0.3% 안팎에서 고HLB와 비율 조절</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↑</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>저HLB→지방 부분응집(건조·크리미·용해지연)</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2740,48 +2782,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>슈가에스터 S-1670</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>ING.sucrose_ester_s1670</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.05</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>0.25</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 고HLB. DMG95 와 페어링</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 고HLB. DMG95 와 페어링</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>고HLB→미세 유화(저HLB와 페어링)</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2789,48 +2832,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>S-1170 / 레시틴 / Soyacell</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>S-1170</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>ING.sucrose_ester_s1170</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>0.05</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>0.25</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 중HLB 보조</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 중HLB 보조</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2838,48 +2882,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>S-1170 / 레시틴 / Soyacell</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>레시틴</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>ING.lecithin</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>0.1</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>0.5</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↑</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2887,48 +2932,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>S-1170 / 레시틴 / Soyacell</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Soyacell</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>ING.soyacell</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>0.1</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>0.5</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 보류] 실사용해 본 적 없는 재료. 우선 보류 · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2936,48 +2982,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>에멀에이드 / 현미호분추출분말</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>에멀에이드</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>ING.emulaid</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.1</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>0.5</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 보조 유화</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 보조 유화</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2985,48 +3032,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>에멀에이드 / 현미호분추출분말</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>현미호분추출분말</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>ING.rice_bran_emulsifier</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>0.5</v>
       </c>
-      <c r="G53" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 현미호분추출분말 — 유화 겸 풍미. 음료 실측에서 1.2~2.5% 사용</t>
-        </is>
+      <c r="H53" t="n">
+        <v>5</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 값 수정] 에멀에이드와 현미호분추출분말은 다른 재료임. 이 칸은 에멀에이드로 변경 · 이전: 표준 사용량(초안) — 검토 필요 · 현미호분추출분말 — 유화 겸 풍미. 음료 실측에서 1.2~2.5% 사용</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3034,48 +3082,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>폴리소르베이트80</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>ING.polysorbate_80</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>제한</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.02</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>0.08</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 매우 강력하나 라벨 이슈. 쓴다면 극소량</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>creaminess↑</t>
+          <t>[검토 2026-08-31 · 보류] 식품업계에서는 잘 쓰이지 않음. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 매우 강력하나 라벨 이슈. 쓴다면 극소량</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>매우 강력하나 라벨 이슈</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3083,48 +3132,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>이눌린</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>ING.inulin</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>8</v>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 섬유·fat replacer. 과하면 소화 불편</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t>[검토 2026-08-31 · 보류] 제조사에 따라 성능 편차가 큼 · 이전: 표준 사용량(초안) — 검토 필요 · 섬유·fat replacer. 과하면 소화 불편</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>섬유·fat replacer·바디(저당 고형분)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3132,48 +3182,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>폴리덱스트로스</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>ING.polydextrose</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>2</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>8</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 벌킹·약한 FPD. 같은 이유로 상한</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>벌킹·약한 FPD</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3181,48 +3232,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>난소화성 말토덱스트린</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>ING.resistant_maltodextrin</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>2</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>8</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 가용성 섬유. 당류 미산입</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>가용성 섬유·바디(당 아님)</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3230,48 +3282,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>결정셀룰로오스(MCC)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>ING.microcrystalline_cellulose</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.2</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>1</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · heat-shock 저항·fat-like</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>heat-shock/용해저항·fat-like</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3279,48 +3332,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>말토덱스트린 / 덱스트린</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>말토덱스트린</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>ING.maltodextrin</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>8</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 고형분. GI 유의</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>creaminess↑ body↑</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>creaminess↑ hardness↓ body↑</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3328,48 +3382,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>말토덱스트린 / 덱스트린</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>덱스트린</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>ING.dextrin</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>2</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>8</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 고형분</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3377,44 +3432,45 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>바닐라 추출물</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>ING.vanilla_extract</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>0.1</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>0.6</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 기본 향</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
         <is>
           <t>기본 향</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3422,48 +3478,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>현미 추출분말</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>ING.brown_rice_extract_powder</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>0.5</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>3</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 쌀 풍미 보강</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>쌀 풍미 보강(base와 별개시)</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3471,44 +3528,45 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>소금</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>ING.salt</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>0.05</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
+      <c r="H63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[검토 2026-08-31 · 값 수정] 소금에 상한폭을 두는 이유는 이해하기 힘들다. · 이전: 표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
         <is>
           <t>풍미증진·리치니스↑(소량)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3516,48 +3574,49 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>딸기퓨레 / 딸기향</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>딸기퓨레</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>ING.strawberry_puree</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>5</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>15</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시. 수분·당을 동반</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3565,44 +3624,45 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
         <is>
           <t>풍미</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>딸기퓨레 / 딸기향</t>
-        </is>
-      </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>딸기향</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>ING.strawberry_artificial</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>0.05</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>0.3</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>ID 확인 필요</t>
         </is>
@@ -3614,36 +3674,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>구연산/무수구연산/젖산</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>구연산</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>ING.citric_acid</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3651,36 +3712,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>구연산/무수구연산/젖산</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>무수구연산</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>ING.citric_acid_anhydrous</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3688,36 +3750,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>구연산/무수구연산/젖산</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>젖산</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>ING.lactic_acid</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3725,36 +3788,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>탄산칼슘/젖산칼슘/구연산나트륨</t>
-        </is>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>탄산칼슘</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>ING.calcium_carbonate</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3762,36 +3826,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>탄산칼슘/젖산칼슘/구연산나트륨</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>젖산칼슘</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>ING.calcium_lactate</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3799,40 +3864,41 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>탄산칼슘/젖산칼슘/구연산나트륨</t>
-        </is>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>구연산나트륨</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>ING.sodium_citrate</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>icy↓</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
+          <t>creaminess↑ icy↓</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3840,36 +3906,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>소브산칼륨</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>ING.potassium_sorbate</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
         <is>
           <t>보존제(미생물) — 물성 후 단계</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3877,36 +3944,37 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
         <is>
           <t>제외/후순위</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>식물추출물(무효과)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>ING.plant_extract</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
         <is>
           <t>관능·물성 효과 없음</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3932,7 +4000,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3940,7 +4007,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -3983,7 +4049,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -4005,7 +4070,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -4048,7 +4112,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -4077,7 +4140,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>

--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1098,49 +1098,52 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>저당</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>필수 base</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>쌀 농축액 (rice extract)</t>
+          <t>설탕</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ING.rice_extract</t>
+          <t>ING.sucrose</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HANDOFF §3.3 · 필수 base 13% 고정 부근</t>
+          <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓ body↑</t>
+          <t>sweet↑ hardness↓</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>제품 필수 base — 쌀 풍미+고형분. 내재 당류량 확정 필요(저당 회계)</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1148,49 +1151,52 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>저당</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>지방(유지)</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>코코넛오일</t>
+          <t>물엿</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ING.coconut_oil</t>
+          <t>ING.glucose_syrup</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 유지방 대체 주력. 6% 미만이면 크리미가 안 서고, 14% 넘으면 기름진 느낌</t>
+          <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>creaminess↑ body↑</t>
+          <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1198,49 +1204,52 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>저당</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>지방(유지)</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>정제야자유</t>
+          <t>쌀조청</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ING.refined_coconut_oil</t>
+          <t>ING.rice_syrup</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HANDOFF §3.3 · iter0 레버 정제야자유</t>
+          <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>creaminess↑ body↑</t>
+          <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1248,49 +1257,52 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>저당</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>지방(유지)</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>하이 팻 파우더</t>
+          <t>포도당</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ING.high_fat_powder</t>
+          <t>ING.dextrose</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 분말지방. 믹스 편의</t>
+          <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>creaminess↑ body↑</t>
+          <t>sweet↑ hardness↓</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>분말지방; 믹스 편의·크리미</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1301,43 +1313,43 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>지방(유지)</t>
+          <t>필수 base</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비건크리머</t>
+          <t>쌀 농축액 (rice extract)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ING.vegan_creamer</t>
+          <t>ING.rice_extract</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>필수</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 지방+유화 겸. 당을 소량 동반</t>
+          <t>HANDOFF §3.3 · 필수 base 13% 고정 부근</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓ body↑</t>
+          <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
+          <t>제품 필수 base — 쌀 풍미+고형분. 내재 당류량 확정 필요(저당 회계)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1356,12 +1368,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>프리마</t>
+          <t>코코넛오일</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ING.prima_creamer</t>
+          <t>ING.coconut_oil</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1370,24 +1382,24 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 프리마. 당 소량 기여를 저당 회계에 반영할 것</t>
+          <t>표준 사용량(초안) — 검토 필요 · 유지방 대체 주력. 6% 미만이면 크리미가 안 서고, 14% 넘으면 기름진 느낌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓ body↑</t>
+          <t>creaminess↑ body↑</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
+          <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1406,12 +1418,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>팜핵경화유</t>
+          <t>정제야자유</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ING.hydrogenated_palm_kernel_oil</t>
+          <t>ING.refined_coconut_oil</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1420,14 +1432,14 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 경질지방 — 소량 구조재. 과하면 왁시</t>
+          <t>HANDOFF §3.3 · iter0 레버 정제야자유</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1437,7 +1449,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>경질지방→용해저항·구조(소량 구조재)</t>
+          <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1456,28 +1468,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>팜 정제유</t>
+          <t>하이 팻 파우더</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ING.palm_oil</t>
+          <t>ING.high_fat_powder</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 범용 식물지방. 코코넛유보다 보조 위치</t>
+          <t>표준 사용량(초안) — 검토 필요 · 분말지방. 믹스 편의</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1487,7 +1499,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>범용 식물지방</t>
+          <t>분말지방; 믹스 편의·크리미</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1506,38 +1518,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>현미유</t>
+          <t>비건크리머</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ING.rice_bran_oil</t>
+          <t>ING.vegan_creamer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · PUFA 산화 관리 필요 — 상한을 낮게</t>
+          <t>표준 사용량(초안) — 검토 필요 · 지방+유화 겸. 당을 소량 동반</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>creaminess↑ body↑</t>
+          <t>creaminess↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>쌀 뉘앙스 보강 가능; PUFA 산화 관리 필요</t>
+          <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1556,38 +1568,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>고올레산 해바라기유</t>
+          <t>프리마</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ING.high_oleic_sunflower_oil</t>
+          <t>ING.prima_creamer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 산화안정 좋은 액상유</t>
+          <t>표준 사용량(초안) — 검토 필요 · 프리마. 당 소량 기여를 저당 회계에 반영할 것</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>creaminess↑ body↑</t>
+          <t>creaminess↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>산화안정 좋은 액상유</t>
+          <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1606,28 +1618,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>일반 해바라기유</t>
+          <t>팜핵경화유</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ING.sunflower_oil</t>
+          <t>ING.hydrogenated_palm_kernel_oil</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 산화 취약 — 산화취 위험. 고올레산형으로 대체 권장</t>
+          <t>표준 사용량(초안) — 검토 필요 · 경질지방 — 소량 구조재. 과하면 왁시</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1637,7 +1649,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>산화 취약 — 산화취 위험, 지양</t>
+          <t>경질지방→용해저항·구조(소량 구조재)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1656,22 +1668,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>생크림</t>
+          <t>팜 정제유</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ING.cream</t>
+          <t>ING.palm_oil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 범용 식물지방. 코코넛유보다 보조 위치</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
@@ -1679,7 +1699,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>동물성(비건 아님)</t>
+          <t>범용 식물지방</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1693,43 +1713,43 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>감미/빙점</t>
+          <t>지방(유지)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>알룰로스</t>
+          <t>현미유</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ING.allulose</t>
+          <t>ING.rice_bran_oil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HANDOFF §3.3 · iter0 레버 알룰로스</t>
+          <t>표준 사용량(초안) — 검토 필요 · PUFA 산화 관리 필요 — 상한을 낮게</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓ body↑</t>
+          <t>creaminess↑ body↑</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>저당 linchpin — 단맛+바디+빙점강하, 쿨링 없음</t>
+          <t>쌀 뉘앙스 보강 가능; PUFA 산화 관리 필요</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1743,17 +1763,17 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>감미/빙점</t>
+          <t>지방(유지)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>에리스리톨</t>
+          <t>고올레산 해바라기유</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ING.erythritol</t>
+          <t>ING.high_oleic_sunflower_oil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1762,24 +1782,24 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · 8% 넘으면 쿨링 오프노트가 뚜렷해진다(HANDOFF 경고)</t>
+          <t>표준 사용량(초안) — 검토 필요 · 산화안정 좋은 액상유</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓ body↑</t>
+          <t>creaminess↑ body↑</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>보조 감미·FPD; 쿨링 오프노트 주의</t>
+          <t>산화안정 좋은 액상유</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1793,43 +1813,43 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>감미/빙점</t>
+          <t>지방(유지)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>고감미도 감미료</t>
+          <t>일반 해바라기유</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ING.high_intensity_sweetener</t>
+          <t>ING.sunflower_oil</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08</v>
+        <v>8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 삭제] HIS는 쪼개기로 했었지.</t>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 산화 취약 — 산화취 위험. 고올레산형으로 대체 권장</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓</t>
+          <t>creaminess↑ body↑</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>단맛 보강 극소량(벌크·FPD 없음)</t>
+          <t>산화 취약 — 산화취 위험, 지양</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1843,43 +1863,35 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>감미/빙점</t>
+          <t>지방(유지)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>설탕</t>
+          <t>생크림</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ING.sucrose</t>
+          <t>ING.cream</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>제한</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" t="n">
-        <v>25</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[검토 2026-08-31 · 값 수정] 목적에 따라 상한/하한이 바뀐다. 지금껀 일반 아이스크림 기준으로, 저당 아이스크림은 상한이 5, 하한은 0이된다. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 저당 목표와 상충하나 FPD·바디 목적 최소량은 필요할 수 있다</t>
-        </is>
-      </c>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓</t>
+          <t>creaminess↑ body↑</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+          <t>동물성(비건 아님)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -1898,28 +1910,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>물엿</t>
+          <t>알룰로스</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ING.glucose_syrup</t>
+          <t>ING.allulose</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 같은 이유</t>
+          <t>HANDOFF §3.3 · iter0 레버 알룰로스</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1929,7 +1941,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+          <t>저당 linchpin — 단맛+바디+빙점강하, 쿨링 없음</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -1948,38 +1960,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>포도당</t>
+          <t>에리스리톨</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ING.dextrose</t>
+          <t>ING.erythritol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. FPD 가 설탕보다 강해 소량으로도 효과</t>
+          <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · 8% 넘으면 쿨링 오프노트가 뚜렷해진다(HANDOFF 경고)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓</t>
+          <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+          <t>보조 감미·FPD; 쿨링 오프노트 주의</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -1998,38 +2010,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>쌀조청</t>
+          <t>고감미도 감미료</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ING.rice_syrup</t>
+          <t>ING.high_intensity_sweetener</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>제외</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>0.08</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류(쌀조청)</t>
+          <t>[검토 2026-08-31 · 삭제] HIS는 쪼개기로 했었지.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓ body↑</t>
+          <t>sweet↑ hardness↓</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
+          <t>단맛 보강 극소량(벌크·FPD 없음)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2043,43 +2055,43 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>단백</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>분리대두단백</t>
+          <t>설탕</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ING.soy_protein_isolate</t>
+          <t>ING.sucrose</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 유화·기포·바디. 3.5% 넘으면 콩 오프노트</t>
+          <t>[검토 2026-08-31 · 값 수정] 목적에 따라 상한/하한이 바뀐다. 지금껀 일반 아이스크림 기준으로, 저당 아이스크림은 상한이 5, 하한은 0이된다. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 저당 목표와 상충하나 FPD·바디 목적 최소량은 필요할 수 있다</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>hardness↓ body↑</t>
+          <t>sweet↑ hardness↓</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>유화·기포·바디 (단백 결론: 대두단백)</t>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2093,43 +2105,43 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>단백</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>완두단백</t>
+          <t>물엿</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ING.pea_protein_isolate</t>
+          <t>ING.glucose_syrup</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 대체 식물단백. 오프노트는 대두보다 강한 편</t>
+          <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 같은 이유</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>hardness↓ body↑</t>
+          <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>대체 식물단백</t>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2143,17 +2155,17 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>단백</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>쌀단백</t>
+          <t>포도당</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ING.rice_protein</t>
+          <t>ING.dextrose</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2162,24 +2174,24 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 보류] 쌀단백은 공급사에 따라 편차가 굉장히 큰 재료. 일단 보류 후 데이터에 의존 · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 가용성 낮고 그릿티 — 대두단백으로 대체 결론(HANDOFF)</t>
+          <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. FPD 가 설탕보다 강해 소량으로도 효과</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>hardness↓ body↑</t>
+          <t>sweet↑ hardness↓</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>가용성 낮음·그릿티 → 대두로 대체</t>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2193,35 +2205,43 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>단백</t>
+          <t>감미/빙점</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>탈지분유</t>
+          <t>쌀조청</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ING.skim_milk_powder</t>
+          <t>ING.rice_syrup</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류(쌀조청)</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>hardness↓ body↑</t>
+          <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>동물성(비건 아님)</t>
+          <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2235,17 +2255,17 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>안정제</t>
+          <t>단백</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>구아검</t>
+          <t>분리대두단백</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ING.guar_gum</t>
+          <t>ING.soy_protein_isolate</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2254,24 +2274,24 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.35</v>
+        <v>3.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>HANDOFF §3.3 · iter0 레버 구아검</t>
+          <t>표준 사용량(초안) — 검토 필요 · 유화·기포·바디. 3.5% 넘으면 콩 오프노트</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>creaminess↑ icy↓ body↑</t>
+          <t>hardness↓ body↑</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>얼음결정 억제 주력</t>
+          <t>유화·기포·바디 (단백 결론: 대두단백)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2285,43 +2305,43 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>안정제</t>
+          <t>단백</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>로커스트빈검(LBG)</t>
+          <t>완두단백</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ING.locust_bean_gum</t>
+          <t>ING.pea_protein_isolate</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 구아와 시너지. 0.3% 넘으면 검성</t>
+          <t>표준 사용량(초안) — 검토 필요 · 대체 식물단백. 오프노트는 대두보다 강한 편</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>creaminess↑ icy↓ body↑</t>
+          <t>hardness↓ body↑</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>구아와 시너지·크리미</t>
+          <t>대체 식물단백</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2335,43 +2355,43 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>안정제</t>
+          <t>단백</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>카라기난</t>
+          <t>쌀단백</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ING.carrageenan</t>
+          <t>ING.rice_protein</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 2차 안정제 — 유청분리 방지용 극소량</t>
+          <t>[검토 2026-08-31 · 보류] 쌀단백은 공급사에 따라 편차가 굉장히 큰 재료. 일단 보류 후 데이터에 의존 · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 가용성 낮고 그릿티 — 대두단백으로 대체 결론(HANDOFF)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>creaminess↑ icy↓ body↑</t>
+          <t>hardness↓ body↑</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>서스펜션·바디(유청분리 방지)</t>
+          <t>가용성 낮음·그릿티 → 대두로 대체</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2385,43 +2405,35 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>안정제</t>
+          <t>단백</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>람다</t>
+          <t>탈지분유</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ING.lambda_carrageenan</t>
+          <t>ING.skim_milk_powder</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>표준 사용량(초안) — 검토 필요 · 같은 역할. 겔화 안 하는 형</t>
-        </is>
-      </c>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>creaminess↑ icy↓ body↑</t>
+          <t>hardness↓ body↑</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>서스펜션·바디(유청분리 방지)</t>
+          <t>동물성(비건 아님)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2440,12 +2452,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AnyAddy An15 (HPMC)</t>
+          <t>구아검</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ING.anyaddy_an15</t>
+          <t>ING.guar_gum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2454,24 +2466,24 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>0.35</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · HPMC. 오버런·용해저항·동결해동</t>
+          <t>HANDOFF §3.3 · iter0 레버 구아검</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓ icy↓</t>
+          <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>오버런·용해저항·동결해동 안정</t>
+          <t>얼음결정 억제 주력</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2490,28 +2502,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>잔탄검</t>
+          <t>로커스트빈검(LBG)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ING.xanthan_gum</t>
+          <t>ING.locust_bean_gum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 온톨로지 limitations: '&gt; ~0.5% -&gt; slimy/stringy'. 그보다 훨씬 낮게 잡음</t>
+          <t>표준 사용량(초안) — 검토 필요 · 구아와 시너지. 0.3% 넘으면 검성</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2521,7 +2533,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>소량 점도(과량시 검성 주의)</t>
+          <t>구아와 시너지·크리미</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2540,28 +2552,28 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>카라기난</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ING.cmc</t>
+          <t>ING.carrageenan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 점도·수분결합</t>
+          <t>표준 사용량(초안) — 검토 필요 · 2차 안정제 — 유청분리 방지용 극소량</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2571,7 +2583,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>점도·수분결합</t>
+          <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2590,28 +2602,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>겔란검</t>
+          <t>람다</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ING.gellan_gum</t>
+          <t>ING.lambda_carrageenan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 극소량 구조. 과하면 부서지는 겔</t>
+          <t>표준 사용량(초안) — 검토 필요 · 같은 역할. 겔화 안 하는 형</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2621,7 +2633,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>겔화, 극소량 구조</t>
+          <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2640,38 +2652,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>변성전분</t>
+          <t>AnyAddy An15 (HPMC)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ING.modified_starch</t>
+          <t>ING.anyaddy_an15</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 바디·fat replacer. 과하면 전분 느낌</t>
+          <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · HPMC. 오버런·용해저항·동결해동</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>creaminess↑ icy↓ body↑</t>
+          <t>creaminess↑ hardness↓ icy↓</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>바디·fat replacer</t>
+          <t>오버런·용해저항·동결해동 안정</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2685,43 +2697,43 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>유화제</t>
+          <t>안정제</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>모노디글리세라이드(MDG)</t>
+          <t>잔탄검</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ING.mono_diglycerides</t>
+          <t>ING.xanthan_gum</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 아이스크림 표준 유화제</t>
+          <t>표준 사용량(초안) — 검토 필요 · 온톨로지 limitations: '&gt; ~0.5% -&gt; slimy/stringy'. 그보다 훨씬 낮게 잡음</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↑</t>
+          <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>아이스크림 표준 유화제(식물성 선택)</t>
+          <t>소량 점도(과량시 검성 주의)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -2735,43 +2747,43 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>유화제</t>
+          <t>안정제</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DMG95</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ING.dmg95</t>
+          <t>ING.cmc</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 저HLB. 총량 0.3% 안팎에서 고HLB와 비율 조절</t>
+          <t>표준 사용량(초안) — 검토 필요 · 점도·수분결합</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↑</t>
+          <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>저HLB→지방 부분응집(건조·크리미·용해지연)</t>
+          <t>점도·수분결합</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -2785,43 +2797,43 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>유화제</t>
+          <t>안정제</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>슈가에스터 S-1670</t>
+          <t>겔란검</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ING.sucrose_ester_s1670</t>
+          <t>ING.gellan_gum</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H48" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 고HLB. DMG95 와 페어링</t>
+          <t>표준 사용량(초안) — 검토 필요 · 극소량 구조. 과하면 부서지는 겔</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓</t>
+          <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>고HLB→미세 유화(저HLB와 페어링)</t>
+          <t>겔화, 극소량 구조</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -2835,17 +2847,17 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>유화제</t>
+          <t>안정제</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>S-1170</t>
+          <t>변성전분</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ING.sucrose_ester_s1170</t>
+          <t>ING.modified_starch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2854,24 +2866,24 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 중HLB 보조</t>
+          <t>표준 사용량(초안) — 검토 필요 · 바디·fat replacer. 과하면 전분 느낌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓</t>
+          <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>중HLB·클린라벨 보조 유화</t>
+          <t>바디·fat replacer</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -2890,28 +2902,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>레시틴</t>
+          <t>모노디글리세라이드(MDG)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ING.lecithin</t>
+          <t>ING.mono_diglycerides</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>0.1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 아이스크림 표준 유화제</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2921,7 +2933,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>중HLB·클린라벨 보조 유화</t>
+          <t>아이스크림 표준 유화제(식물성 선택)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -2940,38 +2952,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Soyacell</t>
+          <t>DMG95</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ING.soyacell</t>
+          <t>ING.dmg95</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 보류] 실사용해 본 적 없는 재료. 우선 보류 · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 저HLB. 총량 0.3% 안팎에서 고HLB와 비율 조절</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓</t>
+          <t>creaminess↑ hardness↑</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>중HLB·클린라벨 보조 유화</t>
+          <t>저HLB→지방 부분응집(건조·크리미·용해지연)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -2990,28 +3002,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>에멀에이드</t>
+          <t>슈가에스터 S-1670</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ING.emulaid</t>
+          <t>ING.sucrose_ester_s1670</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 보조 유화</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 고HLB. DMG95 와 페어링</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3021,7 +3033,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>보조 유화(현미분말은 풍미 겸)</t>
+          <t>고HLB→미세 유화(저HLB와 페어링)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3040,12 +3052,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>현미호분추출분말</t>
+          <t>S-1170</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ING.rice_bran_emulsifier</t>
+          <t>ING.sucrose_ester_s1170</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3054,14 +3066,14 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 값 수정] 에멀에이드와 현미호분추출분말은 다른 재료임. 이 칸은 에멀에이드로 변경 · 이전: 표준 사용량(초안) — 검토 필요 · 현미호분추출분말 — 유화 겸 풍미. 음료 실측에서 1.2~2.5% 사용</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 중HLB 보조</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3071,7 +3083,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>보조 유화(현미분말은 풍미 겸)</t>
+          <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3090,38 +3102,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>폴리소르베이트80</t>
+          <t>레시틴</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ING.polysorbate_80</t>
+          <t>ING.lecithin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 보류] 식품업계에서는 잘 쓰이지 않음. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 매우 강력하나 라벨 이슈. 쓴다면 극소량</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓</t>
+          <t>creaminess↑ hardness↑</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>매우 강력하나 라벨 이슈</t>
+          <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3135,17 +3147,17 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>벌킹/섬유</t>
+          <t>유화제</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>이눌린</t>
+          <t>Soyacell</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ING.inulin</t>
+          <t>ING.soyacell</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3154,24 +3166,24 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 보류] 제조사에 따라 성능 편차가 큼 · 이전: 표준 사용량(초안) — 검토 필요 · 섬유·fat replacer. 과하면 소화 불편</t>
+          <t>[검토 2026-08-31 · 보류] 실사용해 본 적 없는 재료. 우선 보류 · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>creaminess↑ body↑</t>
+          <t>creaminess↑ hardness↓</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>섬유·fat replacer·바디(저당 고형분)</t>
+          <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3185,43 +3197,43 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>벌킹/섬유</t>
+          <t>유화제</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>폴리덱스트로스</t>
+          <t>에멀에이드</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ING.polydextrose</t>
+          <t>ING.emulaid</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 벌킹·약한 FPD. 같은 이유로 상한</t>
+          <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 보조 유화</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>body↑</t>
+          <t>creaminess↑ hardness↓</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>벌킹·약한 FPD</t>
+          <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3235,43 +3247,43 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>벌킹/섬유</t>
+          <t>유화제</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>난소화성 말토덱스트린</t>
+          <t>현미호분추출분말</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ING.resistant_maltodextrin</t>
+          <t>ING.rice_bran_emulsifier</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 가용성 섬유. 당류 미산입</t>
+          <t>[검토 2026-08-31 · 값 수정] 에멀에이드와 현미호분추출분말은 다른 재료임. 이 칸은 에멀에이드로 변경 · 이전: 표준 사용량(초안) — 검토 필요 · 현미호분추출분말 — 유화 겸 풍미. 음료 실측에서 1.2~2.5% 사용</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>body↑</t>
+          <t>creaminess↑ hardness↓</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>가용성 섬유·바디(당 아님)</t>
+          <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3285,43 +3297,43 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>벌킹/섬유</t>
+          <t>유화제</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>결정셀룰로오스(MCC)</t>
+          <t>폴리소르베이트80</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ING.microcrystalline_cellulose</t>
+          <t>ING.polysorbate_80</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · heat-shock 저항·fat-like</t>
+          <t>[검토 2026-08-31 · 보류] 식품업계에서는 잘 쓰이지 않음. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 매우 강력하나 라벨 이슈. 쓴다면 극소량</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>creaminess↑ icy↓</t>
+          <t>creaminess↑ hardness↓</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>heat-shock/용해저항·fat-like</t>
+          <t>매우 강력하나 라벨 이슈</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3340,12 +3352,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>말토덱스트린</t>
+          <t>이눌린</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ING.maltodextrin</t>
+          <t>ING.inulin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3361,17 +3373,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 고형분. GI 유의</t>
+          <t>[검토 2026-08-31 · 보류] 제조사에 따라 성능 편차가 큼 · 이전: 표준 사용량(초안) — 검토 필요 · 섬유·fat replacer. 과하면 소화 불편</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>creaminess↑ hardness↓ body↑</t>
+          <t>creaminess↑ body↑</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>고형분(말토덱스트린 GI 유의)</t>
+          <t>섬유·fat replacer·바디(저당 고형분)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3390,17 +3402,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>덱스트린</t>
+          <t>폴리덱스트로스</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ING.dextrin</t>
+          <t>ING.polydextrose</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3411,7 +3423,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 고형분</t>
+          <t>표준 사용량(초안) — 검토 필요 · 벌킹·약한 FPD. 같은 이유로 상한</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3421,7 +3433,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>고형분(말토덱스트린 GI 유의)</t>
+          <t>벌킹·약한 FPD</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3435,17 +3447,17 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>풍미</t>
+          <t>벌킹/섬유</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>바닐라 추출물</t>
+          <t>난소화성 말토덱스트린</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ING.vanilla_extract</t>
+          <t>ING.resistant_maltodextrin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3454,20 +3466,24 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 기본 향</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>표준 사용량(초안) — 검토 필요 · 가용성 섬유. 당류 미산입</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>body↑</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>기본 향</t>
+          <t>가용성 섬유·바디(당 아님)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3481,43 +3497,43 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>풍미</t>
+          <t>벌킹/섬유</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>현미 추출분말</t>
+          <t>결정셀룰로오스(MCC)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ING.brown_rice_extract_powder</t>
+          <t>ING.microcrystalline_cellulose</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 쌀 풍미 보강</t>
+          <t>표준 사용량(초안) — 검토 필요 · heat-shock 저항·fat-like</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>body↑</t>
+          <t>creaminess↑ icy↓</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>쌀 풍미 보강(base와 별개시)</t>
+          <t>heat-shock/용해저항·fat-like</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3531,39 +3547,43 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>풍미</t>
+          <t>벌킹/섬유</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>소금</t>
+          <t>말토덱스트린</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ING.salt</t>
+          <t>ING.maltodextrin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>옵션</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[검토 2026-08-31 · 값 수정] 소금에 상한폭을 두는 이유는 이해하기 힘들다. · 이전: 표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>표준 사용량(초안) — 검토 필요 · 고형분. GI 유의</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>creaminess↑ hardness↓ body↑</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>풍미증진·리치니스↑(소량)</t>
+          <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3577,17 +3597,17 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>풍미</t>
+          <t>벌킹/섬유</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>딸기퓨레</t>
+          <t>덱스트린</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ING.strawberry_puree</t>
+          <t>ING.dextrin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3596,24 +3616,24 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시. 수분·당을 동반</t>
+          <t>표준 사용량(초안) — 검토 필요 · 고형분</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>sweet↑ hardness↓</t>
+          <t>body↑</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>딸기 변형 시</t>
+          <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -3632,41 +3652,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>딸기향</t>
+          <t>바닐라 추출물</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ING.strawberry_artificial</t>
+          <t>ING.vanilla_extract</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>옵션</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시</t>
+          <t>표준 사용량(초안) — 검토 필요 · 기본 향</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>딸기 변형 시</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>ID 확인 필요</t>
-        </is>
-      </c>
+          <t>기본 향</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3677,31 +3693,43 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>제외/후순위</t>
+          <t>풍미</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>구연산</t>
+          <t>현미 추출분말</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ING.citric_acid</t>
+          <t>ING.brown_rice_extract_powder</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 쌀 풍미 보강</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>body↑</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>산 — 과일맛 아니면 불필요</t>
+          <t>쌀 풍미 보강(base와 별개시)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -3715,31 +3743,39 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>제외/후순위</t>
+          <t>풍미</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>무수구연산</t>
+          <t>소금</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ING.citric_acid_anhydrous</t>
+          <t>ING.salt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[검토 2026-08-31 · 값 수정] 소금에 상한폭을 두는 이유는 이해하기 힘들다. · 이전: 표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>산 — 과일맛 아니면 불필요</t>
+          <t>풍미증진·리치니스↑(소량)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -3753,31 +3789,43 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>제외/후순위</t>
+          <t>풍미</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>젖산</t>
+          <t>딸기퓨레</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ING.lactic_acid</t>
+          <t>ING.strawberry_puree</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>15</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시. 수분·당을 동반</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>sweet↑ hardness↓</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>산 — 과일맛 아니면 불필요</t>
+          <t>딸기 변형 시</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -3791,34 +3839,46 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>제외/후순위</t>
+          <t>풍미</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>탄산칼슘</t>
+          <t>딸기향</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ING.calcium_carbonate</t>
+          <t>ING.strawberry_artificial</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>pH/칼슘 — 기본 배합 불필요</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
+          <t>딸기 변형 시</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>ID 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3834,12 +3894,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>젖산칼슘</t>
+          <t>구연산</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ING.calcium_lactate</t>
+          <t>ING.citric_acid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3853,7 +3913,7 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>pH/칼슘 — 기본 배합 불필요</t>
+          <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -3872,12 +3932,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>구연산나트륨</t>
+          <t>무수구연산</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ING.sodium_citrate</t>
+          <t>ING.citric_acid_anhydrous</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3888,14 +3948,10 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>creaminess↑ icy↓</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>pH/칼슘 — 기본 배합 불필요</t>
+          <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -3914,12 +3970,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>소브산칼륨</t>
+          <t>젖산</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ING.potassium_sorbate</t>
+          <t>ING.lactic_acid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3933,7 +3989,7 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>보존제(미생물) — 물성 후 단계</t>
+          <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -3952,12 +4008,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>식물추출물(무효과)</t>
+          <t>탄산칼슘</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ING.plant_extract</t>
+          <t>ING.calcium_carbonate</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3971,10 +4027,166 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
+          <t>pH/칼슘 — 기본 배합 불필요</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>제외/후순위</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>젖산칼슘</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ING.calcium_lactate</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>pH/칼슘 — 기본 배합 불필요</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>제외/후순위</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>구연산나트륨</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ING.sodium_citrate</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>creaminess↑ icy↓</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>pH/칼슘 — 기본 배합 불필요</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>제외/후순위</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>소브산칼륨</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ING.potassium_sorbate</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>보존제(미생물) — 물성 후 단계</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>icecream</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>제외/후순위</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>식물추출물(무효과)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ING.plant_extract</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>관능·물성 효과 없음</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
